--- a/data/trans_orig/Q5410A_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5410A_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si necesita  enema o supositorio y es capaz de utilizarlos en 2023</t>
+          <t>Población según si necesita  enema o supositorio y es capaz de utilizarlos en 2023 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>528</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3595</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>940</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>37,46%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -956,97 +956,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>721</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>794</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>556</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>977</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>41,87%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>399</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2392</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>471</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>3736</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>46,3%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2371</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1212</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>5835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -1638,97 +1638,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>952</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2558</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>21,05%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2520</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>2729</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>20,74%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>536</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2758</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>40,99%</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7449</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -2094,97 +2094,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1668</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4682</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>20,86%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>58,56%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1668</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4744</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>20,86%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5222</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>14,28%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>59,33%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1668</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5146</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>14,28%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,86%</t>
         </is>
       </c>
     </row>
@@ -2320,97 +2320,97 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>1078</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>1167</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2433,97 +2433,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3070</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>14,01%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>38,4%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1120</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3636</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>14,01%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3851</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>9,59%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>45,48%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1120</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>9,59%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>533</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4561</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>2420</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>581</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>44,74%</t>
         </is>
       </c>
     </row>
@@ -3002,97 +3002,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1428</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>4855</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>10,63%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>36,16%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>1428</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>5450</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>8,38%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>39,27%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>1428</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>4946</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>8,38%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7747</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2335</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8994</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>52,81%</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2418</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>557</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>996</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>12407</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6687</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14871</t>
+          <t>14510</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>8962</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9308</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17996</t>
+          <t>17598</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>14287</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>24380</t>
+          <t>24673</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,26%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1061</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>406</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>399</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>602</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6563</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15254</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8275</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>18274</t>
+          <t>17947</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,47%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13029</t>
+          <t>13333</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8833</t>
+          <t>8815</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17671</t>
+          <t>17920</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5410A_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5410A_2023-Habitat-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>684</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2239</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>929</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>36,06%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>533</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>54,36%</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>493</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>414</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2392</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1547</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>519</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3138</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,86%</t>
         </is>
       </c>
     </row>
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>12080</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12080</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12080</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>477</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>34,67%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1230</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>8088</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>45,31%</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>592</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>2410</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>592</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>7770</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>43,53%</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1869,12 +1869,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3538</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2028</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,48%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12149</t>
+          <t>13504</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12149</t>
+          <t>13504</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12149</t>
+          <t>13504</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>16244</t>
+          <t>17852</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>16244</t>
+          <t>17852</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16244</t>
+          <t>17852</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1668</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -2202,27 +2202,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>518</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>9794</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,13%</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1252</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>891</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2551,12 +2551,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>6671</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>13037</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>13037</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>13037</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>563</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6195</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>5010</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>8825</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,87%</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>659</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2045</t>
+          <t>2676</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7880</t>
+          <t>9579</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>54,25%</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>663</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>557</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>6236</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>13429</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13429</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>13429</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>19237</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>19237</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>19237</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>790</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>8391</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4980</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12407</t>
+          <t>13078</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>10198</t>
+          <t>10660</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14510</t>
+          <t>15463</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>9740</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>19335</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>20662</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14287</t>
+          <t>15256</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>24673</t>
+          <t>27657</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>44,09%</t>
         </is>
       </c>
     </row>
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>409</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>412</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>15272</t>
+          <t>18232</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>14968</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1634</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7461</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5786</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>13333</t>
+          <t>15167</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>14228</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8815</t>
+          <t>9414</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17920</t>
+          <t>19519</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>42551</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>42551</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>42551</t>
+          <t>47352</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>57033</t>
+          <t>62729</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>57033</t>
+          <t>62729</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>57033</t>
+          <t>62729</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
